--- a/artfynd/A 63437-2025 artfynd.xlsx
+++ b/artfynd/A 63437-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73981835</v>
+        <v>74027436</v>
       </c>
       <c r="B2" t="n">
-        <v>109264</v>
+        <v>107867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>1855</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Hypochoeris maculata. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Anthemis arvensis. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73981404</v>
+        <v>74766063</v>
       </c>
       <c r="B3" t="n">
-        <v>107376</v>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219955</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Arnica montana. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Platanthera chlorantha. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,27 +897,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74027436</v>
+        <v>73981404</v>
       </c>
       <c r="B4" t="n">
-        <v>107338</v>
+        <v>107907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1855</v>
+        <v>219955</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anthemis arvensis</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Anthemis arvensis. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Arnica montana. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,30 +1008,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74153031</v>
+        <v>73981835</v>
       </c>
       <c r="B5" t="n">
-        <v>98589</v>
+        <v>109814</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Dactylorhiza maculata ssp. maculata. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Hypochoeris maculata. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,27 +1119,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74411043</v>
+        <v>75339148</v>
       </c>
       <c r="B6" t="n">
-        <v>106294</v>
+        <v>109815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>220204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1144,16 +1148,20 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knutstorp. 600m SSV Knutstorp, Sm</t>
+          <t>Knutstorp, 600 m SSV, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458717</v>
+        <v>458722</v>
       </c>
       <c r="R6" t="n">
-        <v>6408740</v>
+        <v>6408745</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1178,9 +1186,14 @@
           <t>Hakarp</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Arkiv-F-Jön-0476</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1974-01-01</t>
+          <t>1974-12-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1190,7 +1203,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Fraxinus excelsior. LEG: Roland Carlsson</t>
+          <t>KOO: 7E2c 1408.  LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,6 +1212,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1220,38 +1234,38 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Smålands flora (1978-2007)</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74478329</v>
+        <v>74969799</v>
       </c>
       <c r="B7" t="n">
-        <v>100857</v>
+        <v>110077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,7 +1315,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Hepatica nobilis. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Scorzonera humilis. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,27 +1351,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74604169</v>
+        <v>74411043</v>
       </c>
       <c r="B8" t="n">
-        <v>97543</v>
+        <v>106812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1412,7 +1426,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Lycopodium clavatum. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Fraxinus excelsior. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74766063</v>
+        <v>74843549</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>106155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,21 +1473,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219875</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,7 +1537,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Platanthera chlorantha. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Primula veris. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74843549</v>
+        <v>74604169</v>
       </c>
       <c r="B10" t="n">
-        <v>105644</v>
+        <v>97986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,16 +1584,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1634,7 +1648,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Primula veris. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Lycopodium clavatum. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>74969799</v>
+        <v>74781623</v>
       </c>
       <c r="B11" t="n">
-        <v>109528</v>
+        <v>102559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,16 +1695,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>222133</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1745,7 +1759,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Scorzonera humilis. LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Polygala vulgaris. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,54 +1795,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>75339148</v>
+        <v>74478329</v>
       </c>
       <c r="B12" t="n">
-        <v>108728</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220204</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Knutstorp, 600 m SSV, Sm</t>
+          <t>Knutstorp. 600m SSV Knutstorp, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458722</v>
+        <v>458717</v>
       </c>
       <c r="R12" t="n">
-        <v>6408745</v>
+        <v>6408740</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1855,17 +1860,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>1974-01-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>1974-12-31</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>1974-12-31</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>KOO: 7E2c 1408.  LEG: Roland Carlsson</t>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Hepatica nobilis. LEG: Roland Carlsson</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,7 +1879,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1896,7 +1900,114 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>74153031</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Knutstorp. 600m SSV Knutstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>458717</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6408740</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hakarp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1974-01-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1974-12-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7E2c 1408. SOM: Dactylorhiza maculata ssp. maculata. LEG: Roland Carlsson</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Ängsmark, skogsmark, vägkant</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 63437-2025 artfynd.xlsx
+++ b/artfynd/A 63437-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74027436</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74766063</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73981404</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73981835</t>
         </is>
       </c>
     </row>
@@ -1237,6 +1262,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75339148</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74969799</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74411043</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74843549</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1681,6 +1726,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74604169</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74781623</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74478329</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2010,8 +2070,27 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74153031</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>